--- a/artifacts/tasama-hr/imported/demo-files/soudah/Soudah - Leave Tracker 2026.xlsx
+++ b/artifacts/tasama-hr/imported/demo-files/soudah/Soudah - Leave Tracker 2026.xlsx
@@ -441,7 +441,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5B4636"/>
+        <fgColor rgb="FF321E1E"/>
       </patternFill>
     </fill>
   </fills>

--- a/artifacts/tasama-hr/imported/demo-files/soudah/Soudah - Leave Tracker 2026.xlsx
+++ b/artifacts/tasama-hr/imported/demo-files/soudah/Soudah - Leave Tracker 2026.xlsx
@@ -67,352 +67,352 @@
     <t>SDH-1006</t>
   </si>
   <si>
+    <t>Saad Al Shammari</t>
+  </si>
+  <si>
+    <t>SDH-1007</t>
+  </si>
+  <si>
+    <t>Nasser Al Qahtani</t>
+  </si>
+  <si>
+    <t>SDH-1008</t>
+  </si>
+  <si>
+    <t>Anas Al Qurashi</t>
+  </si>
+  <si>
+    <t>SDH-1009</t>
+  </si>
+  <si>
+    <t>Osama Al Tamimi</t>
+  </si>
+  <si>
+    <t>SDH-1010</t>
+  </si>
+  <si>
+    <t>Amal Al Yami</t>
+  </si>
+  <si>
+    <t>SDH-1011</t>
+  </si>
+  <si>
+    <t>Vikram Chowdhury</t>
+  </si>
+  <si>
+    <t>SDH-1012</t>
+  </si>
+  <si>
+    <t>Fahad Al Anazi</t>
+  </si>
+  <si>
+    <t>SDH-1013</t>
+  </si>
+  <si>
+    <t>Khalid Al Juhani</t>
+  </si>
+  <si>
+    <t>SDH-1014</t>
+  </si>
+  <si>
+    <t>Abdulaziz Al Tamimi</t>
+  </si>
+  <si>
+    <t>SDH-1015</t>
+  </si>
+  <si>
+    <t>Nikhil Menon</t>
+  </si>
+  <si>
+    <t>SDH-1016</t>
+  </si>
+  <si>
+    <t>Noura Al Subaie</t>
+  </si>
+  <si>
+    <t>SDH-1017</t>
+  </si>
+  <si>
+    <t>Hamad Al Sudairi</t>
+  </si>
+  <si>
+    <t>SDH-1018</t>
+  </si>
+  <si>
+    <t>Badr Al Fahad</t>
+  </si>
+  <si>
+    <t>SDH-1019</t>
+  </si>
+  <si>
+    <t>Sami Shawky</t>
+  </si>
+  <si>
+    <t>SDH-1020</t>
+  </si>
+  <si>
+    <t>Haifa Al Asmari</t>
+  </si>
+  <si>
+    <t>SDH-1021</t>
+  </si>
+  <si>
+    <t>Mohammed Al Shehri</t>
+  </si>
+  <si>
+    <t>SDH-1022</t>
+  </si>
+  <si>
+    <t>Saad Al Subaie</t>
+  </si>
+  <si>
+    <t>SDH-1023</t>
+  </si>
+  <si>
+    <t>Ziyad Al Shammari</t>
+  </si>
+  <si>
+    <t>SDH-1024</t>
+  </si>
+  <si>
+    <t>Vikram DSouza</t>
+  </si>
+  <si>
+    <t>SDH-1025</t>
+  </si>
+  <si>
+    <t>Abdulrahman Al Asmari</t>
+  </si>
+  <si>
+    <t>SDH-1026</t>
+  </si>
+  <si>
+    <t>Faisal Al Mutairi</t>
+  </si>
+  <si>
+    <t>SDH-1027</t>
+  </si>
+  <si>
+    <t>Jose Santos</t>
+  </si>
+  <si>
+    <t>SDH-1028</t>
+  </si>
+  <si>
+    <t>Khalid Al Subaie</t>
+  </si>
+  <si>
+    <t>SDH-1029</t>
+  </si>
+  <si>
+    <t>Saad Al Saud</t>
+  </si>
+  <si>
+    <t>SDH-1030</t>
+  </si>
+  <si>
+    <t>Lulwa Al Rasheed</t>
+  </si>
+  <si>
+    <t>SDH-1031</t>
+  </si>
+  <si>
+    <t>Mansour Al Sudairi</t>
+  </si>
+  <si>
+    <t>SDH-1032</t>
+  </si>
+  <si>
+    <t>Badr Al Sheikh</t>
+  </si>
+  <si>
+    <t>SDH-1033</t>
+  </si>
+  <si>
+    <t>Sara Al Otaibi</t>
+  </si>
+  <si>
+    <t>SDH-1034</t>
+  </si>
+  <si>
+    <t>Haifa Al Qurashi</t>
+  </si>
+  <si>
+    <t>SDH-1035</t>
+  </si>
+  <si>
+    <t>Mostafa Gemayel</t>
+  </si>
+  <si>
+    <t>SDH-1036</t>
+  </si>
+  <si>
+    <t>Anas Al Malki</t>
+  </si>
+  <si>
+    <t>SDH-1037</t>
+  </si>
+  <si>
+    <t>Walid Haddad</t>
+  </si>
+  <si>
+    <t>SDH-1038</t>
+  </si>
+  <si>
+    <t>Priya Hossain</t>
+  </si>
+  <si>
+    <t>SDH-1039</t>
+  </si>
+  <si>
+    <t>Deema Al Subaie</t>
+  </si>
+  <si>
+    <t>SDH-1040</t>
+  </si>
+  <si>
+    <t>Badr Al Anazi</t>
+  </si>
+  <si>
+    <t>SDH-1041</t>
+  </si>
+  <si>
+    <t>Abeer Al Juhani</t>
+  </si>
+  <si>
+    <t>Yazeed Al Shammari</t>
+  </si>
+  <si>
+    <t>SDH-1043</t>
+  </si>
+  <si>
+    <t>Bandar Al Rashidi</t>
+  </si>
+  <si>
+    <t>SDH-1044</t>
+  </si>
+  <si>
+    <t>Angela Cruz</t>
+  </si>
+  <si>
+    <t>SDH-1045</t>
+  </si>
+  <si>
+    <t>Nasser Al Muqbel</t>
+  </si>
+  <si>
+    <t>SDH-1046</t>
+  </si>
+  <si>
+    <t>Anas Al Otaibi</t>
+  </si>
+  <si>
+    <t>SDH-1047</t>
+  </si>
+  <si>
+    <t>Hessa Al Subaie</t>
+  </si>
+  <si>
+    <t>SDH-1048</t>
+  </si>
+  <si>
+    <t>Hamad Al Saud</t>
+  </si>
+  <si>
+    <t>SDH-1049</t>
+  </si>
+  <si>
+    <t>Angela Santos</t>
+  </si>
+  <si>
+    <t>SDH-1050</t>
+  </si>
+  <si>
+    <t>Nawaf Al Ghamdi</t>
+  </si>
+  <si>
+    <t>SDH-1051</t>
+  </si>
+  <si>
     <t>Mishari Al Rasheed</t>
   </si>
   <si>
-    <t>SDH-1007</t>
-  </si>
-  <si>
-    <t>Saad Al Shammari</t>
-  </si>
-  <si>
-    <t>SDH-1008</t>
-  </si>
-  <si>
-    <t>Nasser Al Qahtani</t>
-  </si>
-  <si>
-    <t>SDH-1009</t>
-  </si>
-  <si>
-    <t>Anas Al Qurashi</t>
-  </si>
-  <si>
-    <t>SDH-1010</t>
-  </si>
-  <si>
-    <t>Osama Al Tamimi</t>
-  </si>
-  <si>
-    <t>SDH-1011</t>
-  </si>
-  <si>
-    <t>Amal Al Yami</t>
-  </si>
-  <si>
-    <t>SDH-1012</t>
-  </si>
-  <si>
-    <t>Vikram Chowdhury</t>
-  </si>
-  <si>
-    <t>SDH-1013</t>
-  </si>
-  <si>
-    <t>Fahad Al Anazi</t>
-  </si>
-  <si>
-    <t>SDH-1014</t>
-  </si>
-  <si>
-    <t>Khalid Al Juhani</t>
-  </si>
-  <si>
-    <t>SDH-1015</t>
-  </si>
-  <si>
-    <t>Abdulaziz Al Tamimi</t>
-  </si>
-  <si>
-    <t>SDH-1016</t>
-  </si>
-  <si>
-    <t>Nikhil Menon</t>
-  </si>
-  <si>
-    <t>SDH-1017</t>
-  </si>
-  <si>
-    <t>Noura Al Subaie</t>
-  </si>
-  <si>
-    <t>SDH-1018</t>
-  </si>
-  <si>
-    <t>Hamad Al Sudairi</t>
-  </si>
-  <si>
-    <t>SDH-1019</t>
-  </si>
-  <si>
-    <t>Badr Al Fahad</t>
-  </si>
-  <si>
-    <t>SDH-1020</t>
-  </si>
-  <si>
-    <t>Sami Shawky</t>
-  </si>
-  <si>
-    <t>SDH-1021</t>
-  </si>
-  <si>
-    <t>Haifa Al Asmari</t>
-  </si>
-  <si>
-    <t>SDH-1022</t>
-  </si>
-  <si>
-    <t>Mohammed Al Shehri</t>
-  </si>
-  <si>
-    <t>SDH-1023</t>
-  </si>
-  <si>
-    <t>Saad Al Subaie</t>
-  </si>
-  <si>
-    <t>SDH-1024</t>
-  </si>
-  <si>
-    <t>Ziyad Al Shammari</t>
-  </si>
-  <si>
-    <t>SDH-1025</t>
-  </si>
-  <si>
-    <t>Vikram DSouza</t>
-  </si>
-  <si>
-    <t>Abdulrahman Al Asmari</t>
-  </si>
-  <si>
-    <t>SDH-1027</t>
-  </si>
-  <si>
-    <t>Faisal Al Mutairi</t>
-  </si>
-  <si>
-    <t>SDH-1028</t>
-  </si>
-  <si>
-    <t>Jose Santos</t>
-  </si>
-  <si>
-    <t>SDH-1029</t>
-  </si>
-  <si>
-    <t>Khalid Al Subaie</t>
-  </si>
-  <si>
-    <t>SDH-1030</t>
-  </si>
-  <si>
-    <t>Saad Al Saud</t>
-  </si>
-  <si>
-    <t>SDH-1031</t>
-  </si>
-  <si>
-    <t>Lulwa Al Rasheed</t>
-  </si>
-  <si>
-    <t>SDH-1032</t>
-  </si>
-  <si>
-    <t>Mansour Al Sudairi</t>
-  </si>
-  <si>
-    <t>SDH-1033</t>
-  </si>
-  <si>
-    <t>Badr Al Sheikh</t>
-  </si>
-  <si>
-    <t>SDH-1034</t>
-  </si>
-  <si>
-    <t>Sara Al Otaibi</t>
-  </si>
-  <si>
-    <t>SDH-1035</t>
-  </si>
-  <si>
-    <t>Haifa Al Qurashi</t>
-  </si>
-  <si>
-    <t>SDH-1036</t>
-  </si>
-  <si>
-    <t>Mostafa Gemayel</t>
-  </si>
-  <si>
-    <t>SDH-1037</t>
-  </si>
-  <si>
-    <t>Anas Al Malki</t>
-  </si>
-  <si>
-    <t>SDH-1038</t>
-  </si>
-  <si>
-    <t>Walid Haddad</t>
-  </si>
-  <si>
-    <t>SDH-1039</t>
-  </si>
-  <si>
-    <t>Priya Hossain</t>
-  </si>
-  <si>
-    <t>SDH-1040</t>
-  </si>
-  <si>
-    <t>Deema Al Subaie</t>
-  </si>
-  <si>
-    <t>SDH-1041</t>
-  </si>
-  <si>
-    <t>Badr Al Anazi</t>
-  </si>
-  <si>
-    <t>SDH-1042</t>
-  </si>
-  <si>
-    <t>Abeer Al Juhani</t>
-  </si>
-  <si>
-    <t>SDH-1043</t>
-  </si>
-  <si>
-    <t>Yazeed Al Shammari</t>
-  </si>
-  <si>
-    <t>SDH-1044</t>
-  </si>
-  <si>
-    <t>Bandar Al Rashidi</t>
-  </si>
-  <si>
-    <t>SDH-1045</t>
-  </si>
-  <si>
-    <t>Angela Cruz</t>
-  </si>
-  <si>
-    <t>SDH-1046</t>
-  </si>
-  <si>
-    <t>Anas Al Otaibi</t>
-  </si>
-  <si>
-    <t>SDH-1047</t>
-  </si>
-  <si>
-    <t>Hessa Al Subaie</t>
-  </si>
-  <si>
-    <t>SDH-1048</t>
-  </si>
-  <si>
-    <t>Hamad Al Saud</t>
-  </si>
-  <si>
-    <t>SDH-1049</t>
-  </si>
-  <si>
-    <t>Angela Santos</t>
-  </si>
-  <si>
-    <t>SDH-1050</t>
-  </si>
-  <si>
-    <t>Nawaf Al Ghamdi</t>
-  </si>
-  <si>
-    <t>SDH-1051</t>
+    <t>SDH-1052</t>
+  </si>
+  <si>
+    <t>Tarek Abdelaziz</t>
+  </si>
+  <si>
+    <t>SDH-1053</t>
+  </si>
+  <si>
+    <t>Waleed Al Harbi</t>
+  </si>
+  <si>
+    <t>SDH-1054</t>
+  </si>
+  <si>
+    <t>Hani Masri</t>
+  </si>
+  <si>
+    <t>SDH-1055</t>
+  </si>
+  <si>
+    <t>Nasser Al Zahrani</t>
+  </si>
+  <si>
+    <t>SDH-1056</t>
+  </si>
+  <si>
+    <t>Grace Bautista</t>
+  </si>
+  <si>
+    <t>SDH-1057</t>
+  </si>
+  <si>
+    <t>Fahad Al Saud</t>
+  </si>
+  <si>
+    <t>SDH-1058</t>
+  </si>
+  <si>
+    <t>Anas Al Muqbel</t>
+  </si>
+  <si>
+    <t>SDH-1059</t>
+  </si>
+  <si>
+    <t>Ibrahim Al Mutairi</t>
+  </si>
+  <si>
+    <t>SDH-1060</t>
+  </si>
+  <si>
+    <t>Neha Siddiqui</t>
+  </si>
+  <si>
+    <t>SDH-1061</t>
+  </si>
+  <si>
+    <t>Rakan Al Nasser</t>
+  </si>
+  <si>
+    <t>SDH-1062</t>
+  </si>
+  <si>
+    <t>Munira Al Yami</t>
+  </si>
+  <si>
+    <t>SDH-1063</t>
+  </si>
+  <si>
+    <t>Munira Al Asmari</t>
+  </si>
+  <si>
+    <t>SDH-1064</t>
   </si>
   <si>
     <t>Ghadah Al Otaibi</t>
-  </si>
-  <si>
-    <t>SDH-1052</t>
-  </si>
-  <si>
-    <t>Tarek Abdelaziz</t>
-  </si>
-  <si>
-    <t>SDH-1053</t>
-  </si>
-  <si>
-    <t>Waleed Al Harbi</t>
-  </si>
-  <si>
-    <t>SDH-1054</t>
-  </si>
-  <si>
-    <t>Hani Masri</t>
-  </si>
-  <si>
-    <t>SDH-1055</t>
-  </si>
-  <si>
-    <t>Nasser Al Zahrani</t>
-  </si>
-  <si>
-    <t>SDH-1056</t>
-  </si>
-  <si>
-    <t>Grace Bautista</t>
-  </si>
-  <si>
-    <t>SDH-1057</t>
-  </si>
-  <si>
-    <t>Fahad Al Saud</t>
-  </si>
-  <si>
-    <t>SDH-1058</t>
-  </si>
-  <si>
-    <t>Anas Al Muqbel</t>
-  </si>
-  <si>
-    <t>SDH-1059</t>
-  </si>
-  <si>
-    <t>Ibrahim Al Mutairi</t>
-  </si>
-  <si>
-    <t>SDH-1060</t>
-  </si>
-  <si>
-    <t>Neha Siddiqui</t>
-  </si>
-  <si>
-    <t>SDH-1061</t>
-  </si>
-  <si>
-    <t>Rakan Al Nasser</t>
-  </si>
-  <si>
-    <t>SDH-1062</t>
-  </si>
-  <si>
-    <t>Munira Al Yami</t>
-  </si>
-  <si>
-    <t>SDH-1063</t>
-  </si>
-  <si>
-    <t>Munira Al Asmari</t>
-  </si>
-  <si>
-    <t>SDH-1064</t>
-  </si>
-  <si>
-    <t>Nasser Al Muqbel</t>
   </si>
 </sst>
 </file>
@@ -852,10 +852,10 @@
         <v>22.5</v>
       </c>
       <c r="F2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G2" s="1">
-        <v>7.5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -875,10 +875,10 @@
         <v>22.5</v>
       </c>
       <c r="F3">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G3" s="1">
-        <v>18.5</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -898,10 +898,10 @@
         <v>22.5</v>
       </c>
       <c r="F4">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G4" s="1">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -921,10 +921,10 @@
         <v>22.5</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G5" s="1">
-        <v>22.5</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -944,10 +944,10 @@
         <v>22.5</v>
       </c>
       <c r="F6">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G6" s="1">
-        <v>10.5</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -967,10 +967,10 @@
         <v>22.5</v>
       </c>
       <c r="F7">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="G7" s="1">
-        <v>5.5</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -984,16 +984,16 @@
         <v>30</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" s="1">
         <v>22.5</v>
       </c>
       <c r="F8">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1">
-        <v>10.5</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -1004,19 +1004,19 @@
         <v>22</v>
       </c>
       <c r="C9">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E9" s="1">
-        <v>22.5</v>
+        <v>15.75</v>
       </c>
       <c r="F9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G9" s="1">
-        <v>17.5</v>
+        <v>16.75</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1030,16 +1030,16 @@
         <v>21</v>
       </c>
       <c r="D10">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E10" s="1">
         <v>15.75</v>
       </c>
       <c r="F10">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G10" s="1">
-        <v>12.75</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1076,13 +1076,13 @@
         <v>21</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E12" s="1">
         <v>15.75</v>
       </c>
       <c r="F12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G12" s="1">
         <v>10.75</v>
@@ -1099,16 +1099,16 @@
         <v>21</v>
       </c>
       <c r="D13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E13" s="1">
         <v>15.75</v>
       </c>
       <c r="F13">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G13" s="1">
-        <v>15.75</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -1122,16 +1122,16 @@
         <v>21</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E14" s="1">
         <v>15.75</v>
       </c>
       <c r="F14">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G14" s="1">
-        <v>7.75</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1145,7 +1145,7 @@
         <v>21</v>
       </c>
       <c r="D15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E15" s="1">
         <v>15.75</v>
@@ -1154,7 +1154,7 @@
         <v>8</v>
       </c>
       <c r="G15" s="1">
-        <v>12.75</v>
+        <v>10.75</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -1168,16 +1168,16 @@
         <v>21</v>
       </c>
       <c r="D16">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E16" s="1">
         <v>15.75</v>
       </c>
       <c r="F16">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G16" s="1">
-        <v>6.75</v>
+        <v>11.75</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -1191,16 +1191,16 @@
         <v>21</v>
       </c>
       <c r="D17">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E17" s="1">
         <v>15.75</v>
       </c>
       <c r="F17">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G17" s="1">
-        <v>10.75</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -1214,16 +1214,16 @@
         <v>21</v>
       </c>
       <c r="D18">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E18" s="1">
         <v>15.75</v>
       </c>
       <c r="F18">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G18" s="1">
-        <v>5.75</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -1243,10 +1243,10 @@
         <v>15.75</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G19" s="1">
-        <v>20.75</v>
+        <v>11.75</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -1260,16 +1260,16 @@
         <v>21</v>
       </c>
       <c r="D20">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E20" s="1">
         <v>15.75</v>
       </c>
       <c r="F20">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="G20" s="1">
-        <v>5.75</v>
+        <v>11.75</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -1283,16 +1283,16 @@
         <v>21</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E21" s="1">
         <v>15.75</v>
       </c>
       <c r="F21">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G21" s="1">
-        <v>3.75</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -1312,10 +1312,10 @@
         <v>15.75</v>
       </c>
       <c r="F22">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G22" s="1">
-        <v>11.75</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -1335,10 +1335,10 @@
         <v>15.75</v>
       </c>
       <c r="F23">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G23" s="1">
-        <v>3.75</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1352,16 +1352,16 @@
         <v>21</v>
       </c>
       <c r="D24">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E24" s="1">
         <v>15.75</v>
       </c>
       <c r="F24">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G24" s="1">
-        <v>13.75</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -1381,10 +1381,10 @@
         <v>15.75</v>
       </c>
       <c r="F25">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G25" s="1">
-        <v>3.75</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -1398,13 +1398,13 @@
         <v>21</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" s="1">
         <v>15.75</v>
       </c>
       <c r="F26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G26" s="1">
         <v>9.75</v>
@@ -1412,16 +1412,16 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="B27" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C27">
         <v>21</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E27" s="1">
         <v>15.75</v>
@@ -1430,130 +1430,130 @@
         <v>8</v>
       </c>
       <c r="G27" s="1">
-        <v>7.75</v>
+        <v>12.75</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B28" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C28">
         <v>21</v>
       </c>
       <c r="D28">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E28" s="1">
         <v>15.75</v>
       </c>
       <c r="F28">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G28" s="1">
-        <v>6.75</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C29">
         <v>21</v>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E29" s="1">
         <v>15.75</v>
       </c>
       <c r="F29">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G29" s="1">
-        <v>9.75</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B30" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C30">
         <v>21</v>
       </c>
       <c r="D30">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E30" s="1">
         <v>15.75</v>
       </c>
       <c r="F30">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G30" s="1">
-        <v>19.75</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B31" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C31">
         <v>21</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31" s="1">
         <v>15.75</v>
       </c>
       <c r="F31">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G31" s="1">
-        <v>4.75</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B32" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C32">
         <v>21</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E32" s="1">
         <v>15.75</v>
       </c>
       <c r="F32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" s="1">
-        <v>15.75</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B33" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C33">
         <v>21</v>
@@ -1565,70 +1565,70 @@
         <v>15.75</v>
       </c>
       <c r="F33">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G33" s="1">
-        <v>3.75</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B34" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C34">
         <v>21</v>
       </c>
       <c r="D34">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E34" s="1">
         <v>15.75</v>
       </c>
       <c r="F34">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="G34" s="1">
-        <v>3.75</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B35" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C35">
         <v>21</v>
       </c>
       <c r="D35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E35" s="1">
         <v>15.75</v>
       </c>
       <c r="F35">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G35" s="1">
-        <v>10.75</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B36" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C36">
         <v>21</v>
       </c>
       <c r="D36">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E36" s="1">
         <v>15.75</v>
@@ -1637,15 +1637,15 @@
         <v>1</v>
       </c>
       <c r="G36" s="1">
-        <v>16.75</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B37" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C37">
         <v>21</v>
@@ -1665,122 +1665,122 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B38" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C38">
         <v>21</v>
       </c>
       <c r="D38">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E38" s="1">
         <v>15.75</v>
       </c>
       <c r="F38">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G38" s="1">
-        <v>15.75</v>
+        <v>11.75</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B39" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C39">
         <v>21</v>
       </c>
       <c r="D39">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E39" s="1">
         <v>15.75</v>
       </c>
       <c r="F39">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G39" s="1">
-        <v>8.75</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B40" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C40">
         <v>21</v>
       </c>
       <c r="D40">
+        <v>5</v>
+      </c>
+      <c r="E40" s="1">
+        <v>15.75</v>
+      </c>
+      <c r="F40">
         <v>0</v>
       </c>
-      <c r="E40" s="1">
-        <v>15.75</v>
-      </c>
-      <c r="F40">
-        <v>1</v>
-      </c>
       <c r="G40" s="1">
-        <v>14.75</v>
+        <v>20.75</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B41" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C41">
         <v>21</v>
       </c>
       <c r="D41">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E41" s="1">
         <v>15.75</v>
       </c>
       <c r="F41">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G41" s="1">
-        <v>11.75</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B42" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C42">
         <v>21</v>
       </c>
       <c r="D42">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E42" s="1">
         <v>15.75</v>
       </c>
       <c r="F42">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G42" s="1">
-        <v>14.75</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>88</v>
+        <v>61</v>
       </c>
       <c r="B43" t="s">
         <v>89</v>
@@ -1789,16 +1789,16 @@
         <v>21</v>
       </c>
       <c r="D43">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E43" s="1">
         <v>15.75</v>
       </c>
       <c r="F43">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G43" s="1">
-        <v>3.75</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -1812,16 +1812,16 @@
         <v>21</v>
       </c>
       <c r="D44">
+        <v>0</v>
+      </c>
+      <c r="E44" s="1">
+        <v>15.75</v>
+      </c>
+      <c r="F44">
         <v>3</v>
       </c>
-      <c r="E44" s="1">
-        <v>15.75</v>
-      </c>
-      <c r="F44">
-        <v>7</v>
-      </c>
       <c r="G44" s="1">
-        <v>11.75</v>
+        <v>12.75</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -1835,13 +1835,13 @@
         <v>21</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E45" s="1">
         <v>15.75</v>
       </c>
       <c r="F45">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G45" s="1">
         <v>3.75</v>
@@ -1864,10 +1864,10 @@
         <v>15.75</v>
       </c>
       <c r="F46">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G46" s="1">
-        <v>3.75</v>
+        <v>-3.25</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -1887,10 +1887,10 @@
         <v>15.75</v>
       </c>
       <c r="F47">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G47" s="1">
-        <v>7.75</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
@@ -1910,10 +1910,10 @@
         <v>15.75</v>
       </c>
       <c r="F48">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="G48" s="1">
-        <v>-3.25</v>
+        <v>14.75</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -1933,10 +1933,10 @@
         <v>15.75</v>
       </c>
       <c r="F49">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G49" s="1">
-        <v>5.75</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
@@ -1956,10 +1956,10 @@
         <v>15.75</v>
       </c>
       <c r="F50">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G50" s="1">
-        <v>11.75</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
@@ -1979,10 +1979,10 @@
         <v>15.75</v>
       </c>
       <c r="F51">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G51" s="1">
-        <v>9.75</v>
+        <v>13.75</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
@@ -1993,19 +1993,19 @@
         <v>107</v>
       </c>
       <c r="C52">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="D52">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E52" s="1">
-        <v>15.75</v>
+        <v>22.5</v>
       </c>
       <c r="F52">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G52" s="1">
-        <v>12.75</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -2025,10 +2025,10 @@
         <v>15.75</v>
       </c>
       <c r="F53">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G53" s="1">
-        <v>17.75</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
@@ -2048,10 +2048,10 @@
         <v>15.75</v>
       </c>
       <c r="F54">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G54" s="1">
-        <v>5.75</v>
+        <v>19.75</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
@@ -2071,10 +2071,10 @@
         <v>15.75</v>
       </c>
       <c r="F55">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G55" s="1">
-        <v>14.75</v>
+        <v>16.75</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -2094,10 +2094,10 @@
         <v>15.75</v>
       </c>
       <c r="F56">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G56" s="1">
-        <v>20.75</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
@@ -2117,10 +2117,10 @@
         <v>15.75</v>
       </c>
       <c r="F57">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="G57" s="1">
-        <v>19.75</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
@@ -2140,10 +2140,10 @@
         <v>15.75</v>
       </c>
       <c r="F58">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G58" s="1">
-        <v>10.75</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
@@ -2186,10 +2186,10 @@
         <v>15.75</v>
       </c>
       <c r="F60">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G60" s="1">
-        <v>14.75</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
@@ -2209,10 +2209,10 @@
         <v>15.75</v>
       </c>
       <c r="F61">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G61" s="1">
-        <v>9.75</v>
+        <v>13.75</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -2232,10 +2232,10 @@
         <v>15.75</v>
       </c>
       <c r="F62">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G62" s="1">
-        <v>8.75</v>
+        <v>14.75</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
@@ -2255,10 +2255,10 @@
         <v>15.75</v>
       </c>
       <c r="F63">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G63" s="1">
-        <v>11.75</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
@@ -2278,10 +2278,10 @@
         <v>15.75</v>
       </c>
       <c r="F64">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G64" s="1">
-        <v>9.75</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
@@ -2295,16 +2295,16 @@
         <v>21</v>
       </c>
       <c r="D65">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E65" s="1">
         <v>15.75</v>
       </c>
       <c r="F65">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G65" s="1">
-        <v>6.75</v>
+        <v>4.75</v>
       </c>
     </row>
   </sheetData>
